--- a/target/classes/com/mycompany/ocxrst/BASES/CFDI.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/CFDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C5DF12-6C61-4956-AA71-7F6636D74025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A79131-31CF-4D06-93DC-6BC7AF709113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="8170" xr2:uid="{942D0663-1C0A-4C19-91D8-E59AAC6912FB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{942D0663-1C0A-4C19-91D8-E59AAC6912FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>G01 - Adquisición de mercancías</t>
   </si>
@@ -99,18 +99,6 @@
   </si>
   <si>
     <t>D09 - Depósitos en cuentas para ahorro</t>
-  </si>
-  <si>
-    <t>P01 - Por definir</t>
-  </si>
-  <si>
-    <t>S01 - Sin efectos fiscales</t>
-  </si>
-  <si>
-    <t>CP01 - Pagos</t>
-  </si>
-  <si>
-    <t>CN01 - Nómina</t>
   </si>
   <si>
     <t>CFDI</t>
@@ -485,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07996858-D5F7-4754-BCB6-17D6A41F9936}">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.36328125" bestFit="1" customWidth="1"/>
@@ -493,7 +481,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -599,26 +587,6 @@
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/target/classes/com/mycompany/ocxrst/BASES/CFDI.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/CFDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A79131-31CF-4D06-93DC-6BC7AF709113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FF3D42-CFEE-470A-92B9-C1BE78B22475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{942D0663-1C0A-4C19-91D8-E59AAC6912FB}"/>
+    <workbookView xWindow="3120" yWindow="1200" windowWidth="14400" windowHeight="8170" xr2:uid="{942D0663-1C0A-4C19-91D8-E59AAC6912FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>G01 - Adquisición de mercancías</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>CFDI</t>
+  </si>
+  <si>
+    <t>** Selecciona una opción **</t>
   </si>
 </sst>
 </file>
@@ -473,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07996858-D5F7-4754-BCB6-17D6A41F9936}">
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.36328125" bestFit="1" customWidth="1"/>
@@ -486,106 +489,111 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>20</v>
       </c>
     </row>
